--- a/data/2026/cjsl/fall/coney-island-cyclones-united-tigers-2013-14.xlsx
+++ b/data/2026/cjsl/fall/coney-island-cyclones-united-tigers-2013-14.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>
@@ -259,7 +259,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Canceled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/coney-island-cyclones-united-tigers-2013-14.xlsx
+++ b/data/2026/cjsl/fall/coney-island-cyclones-united-tigers-2013-14.xlsx
@@ -294,7 +294,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - Bill Brown 9v9 Full Field</t>
+          <t/>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>TBS</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/coney-island-cyclones-united-tigers-2013-14.xlsx
+++ b/data/2026/cjsl/fall/coney-island-cyclones-united-tigers-2013-14.xlsx
@@ -329,7 +329,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 0</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
